--- a/Experiments/outputs/scenario_3_np.xlsx
+++ b/Experiments/outputs/scenario_3_np.xlsx
@@ -530,55 +530,55 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>363.4484505679453</v>
+        <v>373.1698178520604</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08243918418884277</v>
+        <v>0.2050590515136719</v>
       </c>
       <c r="E2" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H2" t="n">
-        <v>587.1082948177047</v>
+        <v>727.6119320370741</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1926891803741455</v>
+        <v>0.8350131511688232</v>
       </c>
       <c r="J2" t="n">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="K2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L2" t="n">
-        <v>118</v>
+        <v>176</v>
       </c>
       <c r="M2" t="n">
-        <v>1786.40076298092</v>
+        <v>1854.412571594569</v>
       </c>
       <c r="N2" t="n">
-        <v>1.717695951461792</v>
+        <v>1.710081100463867</v>
       </c>
       <c r="O2" t="n">
-        <v>559</v>
+        <v>576</v>
       </c>
       <c r="P2" t="n">
         <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>1456</v>
+        <v>1477</v>
       </c>
       <c r="R2" t="n">
-        <v>0.7965470805322159</v>
+        <v>0.7987665616766285</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6713456985777297</v>
+        <v>0.607632118557406</v>
       </c>
     </row>
     <row r="3">
@@ -591,55 +591,55 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>299.7930197802639</v>
+        <v>350.3857354199212</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1313469409942627</v>
+        <v>0.1881279945373535</v>
       </c>
       <c r="E3" t="n">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="F3" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H3" t="n">
-        <v>652.768245367395</v>
+        <v>610.4348402455042</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4600052833557129</v>
+        <v>0.9183797836303711</v>
       </c>
       <c r="J3" t="n">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="K3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L3" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M3" t="n">
-        <v>1864.57420028853</v>
+        <v>1867.721399078492</v>
       </c>
       <c r="N3" t="n">
-        <v>1.595770835876465</v>
+        <v>1.544854879379272</v>
       </c>
       <c r="O3" t="n">
-        <v>519</v>
+        <v>580</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>1302</v>
+        <v>1480</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8392163638572963</v>
+        <v>0.8123993569957507</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6499102876858514</v>
+        <v>0.6731660082993725</v>
       </c>
     </row>
     <row r="4">
@@ -652,55 +652,55 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>328.2697387201397</v>
+        <v>353.5144457390608</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1228857040405273</v>
+        <v>0.3209660053253174</v>
       </c>
       <c r="E4" t="n">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="F4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H4" t="n">
-        <v>701.0644485834534</v>
+        <v>658.7914650683115</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3399598598480225</v>
+        <v>1.370255947113037</v>
       </c>
       <c r="J4" t="n">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="K4" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="L4" t="n">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="M4" t="n">
-        <v>1891.682748556398</v>
+        <v>1780.804652940126</v>
       </c>
       <c r="N4" t="n">
-        <v>1.497150897979736</v>
+        <v>3.634320735931396</v>
       </c>
       <c r="O4" t="n">
-        <v>543</v>
+        <v>592</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
       </c>
       <c r="Q4" t="n">
-        <v>1399</v>
+        <v>1523</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8264668116413005</v>
+        <v>0.8014861174383137</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6293963937037235</v>
+        <v>0.6300596677009799</v>
       </c>
     </row>
     <row r="5">
@@ -713,55 +713,55 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>330.8932567418725</v>
+        <v>319.3812413013744</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0800471305847168</v>
+        <v>0.3149938583374023</v>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F5" t="n">
         <v>19</v>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H5" t="n">
-        <v>682.2829051188232</v>
+        <v>715.9248007529485</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2600052356719971</v>
+        <v>1.67632794380188</v>
       </c>
       <c r="J5" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="K5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L5" t="n">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="M5" t="n">
-        <v>1867.265645192458</v>
+        <v>1774.765844305353</v>
       </c>
       <c r="N5" t="n">
-        <v>1.342137098312378</v>
+        <v>2.246974945068359</v>
       </c>
       <c r="O5" t="n">
-        <v>530</v>
+        <v>576</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1404</v>
+        <v>1505</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8227926178614144</v>
+        <v>0.8200431666373539</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6346085481326891</v>
+        <v>0.5966088692487976</v>
       </c>
     </row>
     <row r="6">
@@ -774,55 +774,55 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>324.3607177066837</v>
+        <v>375.8978650368034</v>
       </c>
       <c r="D6" t="n">
-        <v>0.08212089538574219</v>
+        <v>0.1857399940490723</v>
       </c>
       <c r="E6" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F6" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G6" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H6" t="n">
-        <v>693.7413542576104</v>
+        <v>545.2171373508504</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2656702995300293</v>
+        <v>0.5647759437561035</v>
       </c>
       <c r="J6" t="n">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="K6" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L6" t="n">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="M6" t="n">
-        <v>1838.44579923959</v>
+        <v>1794.018262857448</v>
       </c>
       <c r="N6" t="n">
-        <v>1.627254009246826</v>
+        <v>1.448905944824219</v>
       </c>
       <c r="O6" t="n">
-        <v>548</v>
+        <v>566</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q6" t="n">
-        <v>1405</v>
+        <v>1472</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8235679736433653</v>
+        <v>0.790471550474583</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6226479156771699</v>
+        <v>0.6960916459777572</v>
       </c>
     </row>
     <row r="7">
@@ -835,55 +835,55 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>333.0795247592052</v>
+        <v>355.2030048107574</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1165049076080322</v>
+        <v>0.166776180267334</v>
       </c>
       <c r="E7" t="n">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="F7" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G7" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H7" t="n">
-        <v>677.5281453759706</v>
+        <v>653.2198802912162</v>
       </c>
       <c r="I7" t="n">
-        <v>0.337334156036377</v>
+        <v>1.886931419372559</v>
       </c>
       <c r="J7" t="n">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="K7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="L7" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M7" t="n">
-        <v>1767.038635237742</v>
+        <v>1814.769601523902</v>
       </c>
       <c r="N7" t="n">
-        <v>1.449404954910278</v>
+        <v>1.715548753738403</v>
       </c>
       <c r="O7" t="n">
-        <v>533</v>
+        <v>557</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>1367</v>
+        <v>1407</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8115041074275142</v>
+        <v>0.8042710190249575</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6165742322409299</v>
+        <v>0.6400535474350612</v>
       </c>
     </row>
     <row r="8">
@@ -896,55 +896,55 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>327.5912192431188</v>
+        <v>325.6673906875473</v>
       </c>
       <c r="D8" t="n">
-        <v>0.08399796485900879</v>
+        <v>0.1492397785186768</v>
       </c>
       <c r="E8" t="n">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="F8" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H8" t="n">
-        <v>684.0281416279863</v>
+        <v>596.6315450367387</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3691048622131348</v>
+        <v>0.5373599529266357</v>
       </c>
       <c r="J8" t="n">
-        <v>145</v>
+        <v>109</v>
       </c>
       <c r="K8" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="L8" t="n">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="M8" t="n">
-        <v>1896.454751662934</v>
+        <v>1800.49357297463</v>
       </c>
       <c r="N8" t="n">
-        <v>1.685754776000977</v>
+        <v>1.460036277770996</v>
       </c>
       <c r="O8" t="n">
-        <v>560</v>
+        <v>582</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1420</v>
+        <v>1537</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8272612521042932</v>
+        <v>0.8191232695435252</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6393121739244313</v>
+        <v>0.6686288948807342</v>
       </c>
     </row>
     <row r="9">
@@ -957,55 +957,55 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>350.374894661028</v>
+        <v>375.7929803017611</v>
       </c>
       <c r="D9" t="n">
-        <v>0.09920597076416016</v>
+        <v>0.1336030960083008</v>
       </c>
       <c r="E9" t="n">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="F9" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G9" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>690.2719052652047</v>
+        <v>683.0811187148122</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2599318027496338</v>
+        <v>0.8429458141326904</v>
       </c>
       <c r="J9" t="n">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="K9" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="L9" t="n">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="M9" t="n">
-        <v>1934.459069432014</v>
+        <v>1819.041029466514</v>
       </c>
       <c r="N9" t="n">
-        <v>1.465019941329956</v>
+        <v>1.438595056533813</v>
       </c>
       <c r="O9" t="n">
-        <v>527</v>
+        <v>555</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>1347</v>
+        <v>1405</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8188770699791011</v>
+        <v>0.7934114875836676</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6431705812892288</v>
+        <v>0.6244828414259873</v>
       </c>
     </row>
     <row r="10">
@@ -1018,55 +1018,55 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>362.8541422813684</v>
+        <v>369.867576787245</v>
       </c>
       <c r="D10" t="n">
-        <v>0.08298301696777344</v>
+        <v>0.1220333576202393</v>
       </c>
       <c r="E10" t="n">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="F10" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H10" t="n">
-        <v>720.3985858017425</v>
+        <v>632.9218454673187</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2666599750518799</v>
+        <v>0.7242240905761719</v>
       </c>
       <c r="J10" t="n">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="K10" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="L10" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="M10" t="n">
-        <v>1805.997125779191</v>
+        <v>1800.754764075535</v>
       </c>
       <c r="N10" t="n">
-        <v>1.490481853485107</v>
+        <v>1.760329008102417</v>
       </c>
       <c r="O10" t="n">
-        <v>542</v>
+        <v>585</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>1428</v>
+        <v>1460</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7990837653604701</v>
+        <v>0.7946041381280886</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6011075679365054</v>
+        <v>0.6485241310511008</v>
       </c>
     </row>
     <row r="11">
@@ -1079,55 +1079,55 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>339.0373356560684</v>
+        <v>374.3963675070286</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1376199722290039</v>
+        <v>0.2011311054229736</v>
       </c>
       <c r="E11" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F11" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G11" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H11" t="n">
-        <v>671.2017012543001</v>
+        <v>683.859323917424</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4287199974060059</v>
+        <v>0.5211977958679199</v>
       </c>
       <c r="J11" t="n">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="K11" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="L11" t="n">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="M11" t="n">
-        <v>1863.292946261788</v>
+        <v>1862.665682168329</v>
       </c>
       <c r="N11" t="n">
-        <v>1.490301847457886</v>
+        <v>1.608482122421265</v>
       </c>
       <c r="O11" t="n">
-        <v>525</v>
+        <v>588</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1390</v>
+        <v>1509</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8180439976782725</v>
+        <v>0.7989996964612599</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6397766102206893</v>
+        <v>0.6328598682715068</v>
       </c>
     </row>
     <row r="12">
@@ -1140,55 +1140,55 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>301.821122327498</v>
+        <v>357.2147055714277</v>
       </c>
       <c r="D12" t="n">
-        <v>0.08504390716552734</v>
+        <v>0.1776549816131592</v>
       </c>
       <c r="E12" t="n">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="F12" t="n">
+        <v>19</v>
+      </c>
+      <c r="G12" t="n">
         <v>13</v>
       </c>
-      <c r="G12" t="n">
-        <v>19</v>
-      </c>
       <c r="H12" t="n">
-        <v>726.1815420948657</v>
+        <v>709.4780333240381</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2869319915771484</v>
+        <v>1.462579011917114</v>
       </c>
       <c r="J12" t="n">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="K12" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="L12" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M12" t="n">
-        <v>1833.620209366159</v>
+        <v>1809.338408112282</v>
       </c>
       <c r="N12" t="n">
-        <v>1.592063903808594</v>
+        <v>1.343399286270142</v>
       </c>
       <c r="O12" t="n">
-        <v>539</v>
+        <v>561</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1423</v>
+        <v>1467</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8353960537815894</v>
+        <v>0.802571644989222</v>
       </c>
       <c r="S12" t="n">
-        <v>0.603962948060062</v>
+        <v>0.6078798581055657</v>
       </c>
     </row>
     <row r="13">
@@ -1201,55 +1201,55 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>314.3631311423867</v>
+        <v>319.2379935618277</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0801851749420166</v>
+        <v>0.1185600757598877</v>
       </c>
       <c r="E13" t="n">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="F13" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H13" t="n">
-        <v>644.7505446092071</v>
+        <v>666.5558615800402</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2392871379852295</v>
+        <v>0.6909658908843994</v>
       </c>
       <c r="J13" t="n">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="K13" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="L13" t="n">
-        <v>137</v>
+        <v>169</v>
       </c>
       <c r="M13" t="n">
-        <v>1814.291838369936</v>
+        <v>1798.445022818238</v>
       </c>
       <c r="N13" t="n">
-        <v>1.435081958770752</v>
+        <v>1.779771089553833</v>
       </c>
       <c r="O13" t="n">
-        <v>518</v>
+        <v>572</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>1320</v>
+        <v>1494</v>
       </c>
       <c r="R13" t="n">
-        <v>0.8267295677056958</v>
+        <v>0.822492214378859</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6446268836283319</v>
+        <v>0.6293710104435</v>
       </c>
     </row>
     <row r="14">
@@ -1262,55 +1262,55 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>343.0333989882141</v>
+        <v>326.4892609503088</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0968470573425293</v>
+        <v>0.1792042255401611</v>
       </c>
       <c r="E14" t="n">
+        <v>101</v>
+      </c>
+      <c r="F14" t="n">
+        <v>17</v>
+      </c>
+      <c r="G14" t="n">
+        <v>13</v>
+      </c>
+      <c r="H14" t="n">
+        <v>644.2792784922854</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.6534850597381592</v>
+      </c>
+      <c r="J14" t="n">
         <v>127</v>
       </c>
-      <c r="F14" t="n">
-        <v>14</v>
-      </c>
-      <c r="G14" t="n">
-        <v>16</v>
-      </c>
-      <c r="H14" t="n">
-        <v>681.3905709938575</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.2428507804870605</v>
-      </c>
-      <c r="J14" t="n">
-        <v>121</v>
-      </c>
       <c r="K14" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="L14" t="n">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="M14" t="n">
-        <v>1838.023931773492</v>
+        <v>1842.094525025024</v>
       </c>
       <c r="N14" t="n">
-        <v>1.410136938095093</v>
+        <v>1.662076950073242</v>
       </c>
       <c r="O14" t="n">
-        <v>529</v>
+        <v>570</v>
       </c>
       <c r="P14" t="n">
         <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>1341</v>
+        <v>1512</v>
       </c>
       <c r="R14" t="n">
-        <v>0.81336837183767</v>
+        <v>0.8227619394580885</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6292809036842135</v>
+        <v>0.650246352866429</v>
       </c>
     </row>
     <row r="15">
@@ -1323,55 +1323,55 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>312.4104215696676</v>
+        <v>344.3961454877584</v>
       </c>
       <c r="D15" t="n">
-        <v>0.08428406715393066</v>
+        <v>0.2004611492156982</v>
       </c>
       <c r="E15" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G15" t="n">
         <v>12</v>
       </c>
       <c r="H15" t="n">
-        <v>718.0835855404791</v>
+        <v>721.3882244587322</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2614531517028809</v>
+        <v>0.9003229141235352</v>
       </c>
       <c r="J15" t="n">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="K15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L15" t="n">
-        <v>151</v>
+        <v>190</v>
       </c>
       <c r="M15" t="n">
-        <v>1853.509040189738</v>
+        <v>1856.781675890673</v>
       </c>
       <c r="N15" t="n">
-        <v>1.739666938781738</v>
+        <v>1.408130884170532</v>
       </c>
       <c r="O15" t="n">
-        <v>538</v>
+        <v>572</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1403</v>
+        <v>1453</v>
       </c>
       <c r="R15" t="n">
-        <v>0.8314492053744249</v>
+        <v>0.8145198490702703</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6125815574835444</v>
+        <v>0.6114846275005962</v>
       </c>
     </row>
     <row r="16">
@@ -1384,55 +1384,55 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>303.1066933967749</v>
+        <v>361.9018764001732</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1136710643768311</v>
+        <v>0.1370902061462402</v>
       </c>
       <c r="E16" t="n">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="F16" t="n">
+        <v>21</v>
+      </c>
+      <c r="G16" t="n">
+        <v>14</v>
+      </c>
+      <c r="H16" t="n">
+        <v>690.5053427401519</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.7535359859466553</v>
+      </c>
+      <c r="J16" t="n">
+        <v>137</v>
+      </c>
+      <c r="K16" t="n">
         <v>17</v>
       </c>
-      <c r="G16" t="n">
-        <v>9</v>
-      </c>
-      <c r="H16" t="n">
-        <v>655.4735471677359</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.3518660068511963</v>
-      </c>
-      <c r="J16" t="n">
-        <v>126</v>
-      </c>
-      <c r="K16" t="n">
-        <v>20</v>
-      </c>
       <c r="L16" t="n">
-        <v>145</v>
+        <v>178</v>
       </c>
       <c r="M16" t="n">
-        <v>1832.377408330697</v>
+        <v>1819.999958537276</v>
       </c>
       <c r="N16" t="n">
-        <v>1.522894859313965</v>
+        <v>1.800512790679932</v>
       </c>
       <c r="O16" t="n">
-        <v>513</v>
+        <v>564</v>
       </c>
       <c r="P16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>1287</v>
+        <v>1472</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8345828255583514</v>
+        <v>0.8011528106346597</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6422824554659431</v>
+        <v>0.6206014513895334</v>
       </c>
     </row>
     <row r="17">
@@ -1445,55 +1445,55 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>339.8828347233909</v>
+        <v>389.2512274738664</v>
       </c>
       <c r="D17" t="n">
-        <v>0.08527994155883789</v>
+        <v>0.2223308086395264</v>
       </c>
       <c r="E17" t="n">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="F17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G17" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H17" t="n">
-        <v>699.864131657322</v>
+        <v>678.5215191454037</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4210100173950195</v>
+        <v>1.048639059066772</v>
       </c>
       <c r="J17" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K17" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L17" t="n">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="M17" t="n">
-        <v>1797.79863968379</v>
+        <v>1779.790141475239</v>
       </c>
       <c r="N17" t="n">
-        <v>1.555887937545776</v>
+        <v>1.644185066223145</v>
       </c>
       <c r="O17" t="n">
-        <v>526</v>
+        <v>561</v>
       </c>
       <c r="P17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>1395</v>
+        <v>1461</v>
       </c>
       <c r="R17" t="n">
-        <v>0.810944992825686</v>
+        <v>0.7812937500871746</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6107105010489834</v>
+        <v>0.6187631882357837</v>
       </c>
     </row>
     <row r="18">
@@ -1506,55 +1506,55 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>307.9918069660094</v>
+        <v>336.3287940631943</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0820457935333252</v>
+        <v>0.160271167755127</v>
       </c>
       <c r="E18" t="n">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="F18" t="n">
         <v>16</v>
       </c>
       <c r="G18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H18" t="n">
-        <v>678.2956616450084</v>
+        <v>601.5129018361282</v>
       </c>
       <c r="I18" t="n">
-        <v>0.283513069152832</v>
+        <v>0.6077229976654053</v>
       </c>
       <c r="J18" t="n">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="K18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L18" t="n">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="M18" t="n">
-        <v>1883.404555658126</v>
+        <v>1806.83760349046</v>
       </c>
       <c r="N18" t="n">
-        <v>1.590427875518799</v>
+        <v>1.460307121276855</v>
       </c>
       <c r="O18" t="n">
-        <v>546</v>
+        <v>571</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>1377</v>
+        <v>1444</v>
       </c>
       <c r="R18" t="n">
-        <v>0.8364707114885434</v>
+        <v>0.8138577626381739</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6398566311166276</v>
+        <v>0.6670907774588476</v>
       </c>
     </row>
     <row r="19">
@@ -1567,55 +1567,55 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>299.2841758737038</v>
+        <v>338.5005976593832</v>
       </c>
       <c r="D19" t="n">
-        <v>0.07631611824035645</v>
+        <v>0.1476080417633057</v>
       </c>
       <c r="E19" t="n">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="F19" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G19" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H19" t="n">
-        <v>642.5931250541818</v>
+        <v>682.5416987255353</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2315750122070312</v>
+        <v>0.680056095123291</v>
       </c>
       <c r="J19" t="n">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="K19" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L19" t="n">
-        <v>137</v>
+        <v>164</v>
       </c>
       <c r="M19" t="n">
-        <v>1872.998783413207</v>
+        <v>1820.631425402323</v>
       </c>
       <c r="N19" t="n">
-        <v>1.37893009185791</v>
+        <v>2.731812953948975</v>
       </c>
       <c r="O19" t="n">
-        <v>522</v>
+        <v>561</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>1357</v>
+        <v>1444</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8402112278320268</v>
+        <v>0.814075164837616</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6569174893519311</v>
+        <v>0.6251071528249013</v>
       </c>
     </row>
     <row r="20">
@@ -1628,55 +1628,55 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>376.3935404771249</v>
+        <v>292.5983589723205</v>
       </c>
       <c r="D20" t="n">
-        <v>0.09318184852600098</v>
+        <v>0.2391848564147949</v>
       </c>
       <c r="E20" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F20" t="n">
+        <v>12</v>
+      </c>
+      <c r="G20" t="n">
         <v>21</v>
       </c>
-      <c r="G20" t="n">
-        <v>18</v>
-      </c>
       <c r="H20" t="n">
-        <v>649.8150430621495</v>
+        <v>628.2694464211065</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3182060718536377</v>
+        <v>1.002856969833374</v>
       </c>
       <c r="J20" t="n">
-        <v>151</v>
+        <v>125</v>
       </c>
       <c r="K20" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="L20" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="M20" t="n">
-        <v>1859.480884750703</v>
+        <v>1808.356568977601</v>
       </c>
       <c r="N20" t="n">
-        <v>1.779171943664551</v>
+        <v>1.662112951278687</v>
       </c>
       <c r="O20" t="n">
-        <v>528</v>
+        <v>562</v>
       </c>
       <c r="P20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>1325</v>
+        <v>1394</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7975813875991593</v>
+        <v>0.8381965349136049</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6505395412283204</v>
+        <v>0.6525743555230846</v>
       </c>
     </row>
     <row r="21">
@@ -1689,55 +1689,55 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>304.7032485240998</v>
+        <v>329.6949330882929</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1062459945678711</v>
+        <v>0.1702201366424561</v>
       </c>
       <c r="E21" t="n">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="F21" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G21" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H21" t="n">
-        <v>662.3932537378957</v>
+        <v>689.3391620755719</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3625941276550293</v>
+        <v>0.7580649852752686</v>
       </c>
       <c r="J21" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="K21" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L21" t="n">
-        <v>161</v>
+        <v>185</v>
       </c>
       <c r="M21" t="n">
-        <v>1837.942886332914</v>
+        <v>1812.609597988663</v>
       </c>
       <c r="N21" t="n">
-        <v>2.718861818313599</v>
+        <v>2.643745899200439</v>
       </c>
       <c r="O21" t="n">
-        <v>544</v>
+        <v>580</v>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q21" t="n">
-        <v>1404</v>
+        <v>1507</v>
       </c>
       <c r="R21" t="n">
-        <v>0.8342150614200818</v>
+        <v>0.8181103457390193</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6396007413160097</v>
+        <v>0.619697941111816</v>
       </c>
     </row>
     <row r="22">
@@ -1750,55 +1750,55 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>340.2642087201493</v>
+        <v>335.460751816755</v>
       </c>
       <c r="D22" t="n">
-        <v>0.09915971755981445</v>
+        <v>0.200850248336792</v>
       </c>
       <c r="E22" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F22" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H22" t="n">
-        <v>699.7060521950561</v>
+        <v>724.1459419156722</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4451398849487305</v>
+        <v>1.295644998550415</v>
       </c>
       <c r="J22" t="n">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="K22" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="L22" t="n">
-        <v>158</v>
+        <v>195</v>
       </c>
       <c r="M22" t="n">
-        <v>1760.304840093961</v>
+        <v>1834.27424803051</v>
       </c>
       <c r="N22" t="n">
-        <v>1.513175964355469</v>
+        <v>1.754906177520752</v>
       </c>
       <c r="O22" t="n">
-        <v>524</v>
+        <v>589</v>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>1344</v>
+        <v>1494</v>
       </c>
       <c r="R22" t="n">
-        <v>0.8067015434088184</v>
+        <v>0.8171152693350273</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6025085904111315</v>
+        <v>0.6052139189692056</v>
       </c>
     </row>
     <row r="23">
@@ -1811,55 +1811,55 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>354.3542511684068</v>
+        <v>335.416901742116</v>
       </c>
       <c r="D23" t="n">
-        <v>0.09081315994262695</v>
+        <v>0.1500611305236816</v>
       </c>
       <c r="E23" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="F23" t="n">
         <v>21</v>
       </c>
       <c r="G23" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H23" t="n">
-        <v>639.5956286061228</v>
+        <v>657.0721480342929</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2375180721282959</v>
+        <v>0.9752850532531738</v>
       </c>
       <c r="J23" t="n">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="K23" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="L23" t="n">
-        <v>131</v>
+        <v>169</v>
       </c>
       <c r="M23" t="n">
-        <v>1848.215299960329</v>
+        <v>1868.360592743186</v>
       </c>
       <c r="N23" t="n">
-        <v>1.859909057617188</v>
+        <v>1.59948992729187</v>
       </c>
       <c r="O23" t="n">
-        <v>536</v>
+        <v>577</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>1449</v>
+        <v>1446</v>
       </c>
       <c r="R23" t="n">
-        <v>0.8082722012007947</v>
+        <v>0.820475285635496</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6539387869909683</v>
+        <v>0.6483162026717986</v>
       </c>
     </row>
     <row r="24">
@@ -1872,55 +1872,55 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>339.1599369146413</v>
+        <v>345.9750337931137</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1132080554962158</v>
+        <v>0.1572260856628418</v>
       </c>
       <c r="E24" t="n">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="F24" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G24" t="n">
+        <v>8</v>
+      </c>
+      <c r="H24" t="n">
+        <v>586.8945222128254</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.6092190742492676</v>
+      </c>
+      <c r="J24" t="n">
+        <v>119</v>
+      </c>
+      <c r="K24" t="n">
         <v>19</v>
       </c>
-      <c r="H24" t="n">
-        <v>662.2026183861283</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.319957971572876</v>
-      </c>
-      <c r="J24" t="n">
-        <v>134</v>
-      </c>
-      <c r="K24" t="n">
-        <v>23</v>
-      </c>
       <c r="L24" t="n">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="M24" t="n">
-        <v>1739.452809237816</v>
+        <v>1818.743515627473</v>
       </c>
       <c r="N24" t="n">
-        <v>2.084224939346313</v>
+        <v>3.364593982696533</v>
       </c>
       <c r="O24" t="n">
-        <v>536</v>
+        <v>557</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>1358</v>
+        <v>1419</v>
       </c>
       <c r="R24" t="n">
-        <v>0.8050191789547585</v>
+        <v>0.8097724990795357</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6193040622491572</v>
+        <v>0.6773077032742879</v>
       </c>
     </row>
     <row r="25">
@@ -1933,55 +1933,55 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>334.613603267484</v>
+        <v>338.5977143010243</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1784169673919678</v>
+        <v>1.482185125350952</v>
       </c>
       <c r="E25" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F25" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G25" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H25" t="n">
-        <v>722.9300482646011</v>
+        <v>688.8657081909695</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4064202308654785</v>
+        <v>1.620249032974243</v>
       </c>
       <c r="J25" t="n">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="K25" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="L25" t="n">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="M25" t="n">
-        <v>1871.760344161883</v>
+        <v>1876.13085695125</v>
       </c>
       <c r="N25" t="n">
-        <v>1.582465887069702</v>
+        <v>2.278563976287842</v>
       </c>
       <c r="O25" t="n">
-        <v>548</v>
+        <v>607</v>
       </c>
       <c r="P25" t="n">
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>1431</v>
+        <v>1545</v>
       </c>
       <c r="R25" t="n">
-        <v>0.8212305307615042</v>
+        <v>0.8195234020876069</v>
       </c>
       <c r="S25" t="n">
-        <v>0.6137699729992372</v>
+        <v>0.6328264067302908</v>
       </c>
     </row>
     <row r="26">
@@ -1994,55 +1994,55 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>302.377758546587</v>
+        <v>308.9001043249369</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1284029483795166</v>
+        <v>0.2256901264190674</v>
       </c>
       <c r="E26" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G26" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H26" t="n">
-        <v>684.6125370799087</v>
+        <v>728.6607055598729</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3597393035888672</v>
+        <v>1.394253969192505</v>
       </c>
       <c r="J26" t="n">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="K26" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L26" t="n">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="M26" t="n">
-        <v>1892.37018029567</v>
+        <v>1793.509276885641</v>
       </c>
       <c r="N26" t="n">
-        <v>1.417486190795898</v>
+        <v>2.181463956832886</v>
       </c>
       <c r="O26" t="n">
-        <v>546</v>
+        <v>600</v>
       </c>
       <c r="P26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>1428</v>
+        <v>1530</v>
       </c>
       <c r="R26" t="n">
-        <v>0.8402121520962973</v>
+        <v>0.8277677688618763</v>
       </c>
       <c r="S26" t="n">
-        <v>0.6382248334874191</v>
+        <v>0.5937234811379599</v>
       </c>
     </row>
     <row r="27">
@@ -2055,55 +2055,55 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>345.5013648635332</v>
+        <v>395.5964347440233</v>
       </c>
       <c r="D27" t="n">
-        <v>0.07463788986206055</v>
+        <v>0.3039169311523438</v>
       </c>
       <c r="E27" t="n">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="F27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H27" t="n">
-        <v>668.7621585910724</v>
+        <v>606.6182831460624</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2637698650360107</v>
+        <v>1.034247875213623</v>
       </c>
       <c r="J27" t="n">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="K27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L27" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="M27" t="n">
-        <v>1833.045797337327</v>
+        <v>1804.353194221417</v>
       </c>
       <c r="N27" t="n">
-        <v>1.764647960662842</v>
+        <v>1.818145036697388</v>
       </c>
       <c r="O27" t="n">
-        <v>519</v>
+        <v>566</v>
       </c>
       <c r="P27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>1393</v>
+        <v>1382</v>
       </c>
       <c r="R27" t="n">
-        <v>0.8115151485219809</v>
+        <v>0.7807544354337321</v>
       </c>
       <c r="S27" t="n">
-        <v>0.635163420596194</v>
+        <v>0.6638029155883642</v>
       </c>
     </row>
     <row r="28">
@@ -2116,55 +2116,55 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>328.3441753277442</v>
+        <v>371.43669057349</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1235871315002441</v>
+        <v>0.1626739501953125</v>
       </c>
       <c r="E28" t="n">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="F28" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H28" t="n">
-        <v>691.1445806093747</v>
+        <v>672.6315497073383</v>
       </c>
       <c r="I28" t="n">
-        <v>0.307175874710083</v>
+        <v>1.037203073501587</v>
       </c>
       <c r="J28" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K28" t="n">
         <v>22</v>
       </c>
       <c r="L28" t="n">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="M28" t="n">
-        <v>1824.225109087215</v>
+        <v>1851.721610839553</v>
       </c>
       <c r="N28" t="n">
-        <v>1.678168773651123</v>
+        <v>1.724309206008911</v>
       </c>
       <c r="O28" t="n">
-        <v>543</v>
+        <v>573</v>
       </c>
       <c r="P28" t="n">
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>1353</v>
+        <v>1493</v>
       </c>
       <c r="R28" t="n">
-        <v>0.8200089595894022</v>
+        <v>0.799410079571797</v>
       </c>
       <c r="S28" t="n">
-        <v>0.6211297733122413</v>
+        <v>0.6367534159725156</v>
       </c>
     </row>
     <row r="29">
@@ -2177,55 +2177,55 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>320.5516792995541</v>
+        <v>309.2656316748402</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1092350482940674</v>
+        <v>0.1428170204162598</v>
       </c>
       <c r="E29" t="n">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="F29" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G29" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H29" t="n">
-        <v>688.5793353805018</v>
+        <v>708.0774766812829</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2690482139587402</v>
+        <v>1.442032098770142</v>
       </c>
       <c r="J29" t="n">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="K29" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L29" t="n">
-        <v>156</v>
+        <v>191</v>
       </c>
       <c r="M29" t="n">
-        <v>1852.870970726866</v>
+        <v>1841.818577532121</v>
       </c>
       <c r="N29" t="n">
-        <v>1.608987808227539</v>
+        <v>1.833853960037231</v>
       </c>
       <c r="O29" t="n">
-        <v>516</v>
+        <v>565</v>
       </c>
       <c r="P29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>1351</v>
+        <v>1502</v>
       </c>
       <c r="R29" t="n">
-        <v>0.8269973007490078</v>
+        <v>0.8320868105862903</v>
       </c>
       <c r="S29" t="n">
-        <v>0.6283716749524239</v>
+        <v>0.6155552532052065</v>
       </c>
     </row>
     <row r="30">
@@ -2238,55 +2238,55 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>307.5330011654443</v>
+        <v>326.7265568255022</v>
       </c>
       <c r="D30" t="n">
-        <v>0.09168910980224609</v>
+        <v>0.1683928966522217</v>
       </c>
       <c r="E30" t="n">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="F30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G30" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H30" t="n">
-        <v>647.3683110666436</v>
+        <v>685.5307671227556</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2788999080657959</v>
+        <v>0.9975857734680176</v>
       </c>
       <c r="J30" t="n">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="K30" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L30" t="n">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="M30" t="n">
-        <v>1863.680421610016</v>
+        <v>1826.212923992813</v>
       </c>
       <c r="N30" t="n">
-        <v>1.461547136306763</v>
+        <v>1.668323993682861</v>
       </c>
       <c r="O30" t="n">
-        <v>526</v>
+        <v>584</v>
       </c>
       <c r="P30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>1346</v>
+        <v>1493</v>
       </c>
       <c r="R30" t="n">
-        <v>0.8349861931265182</v>
+        <v>0.8210906556771317</v>
       </c>
       <c r="S30" t="n">
-        <v>0.6526398498582777</v>
+        <v>0.6246161889907568</v>
       </c>
     </row>
     <row r="31">
@@ -2299,55 +2299,55 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>335.4780581588281</v>
+        <v>321.0487730659916</v>
       </c>
       <c r="D31" t="n">
-        <v>0.09864497184753418</v>
+        <v>0.1438310146331787</v>
       </c>
       <c r="E31" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F31" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G31" t="n">
         <v>11</v>
       </c>
       <c r="H31" t="n">
-        <v>655.1336877089</v>
+        <v>716.5358654191197</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2947978973388672</v>
+        <v>0.8819630146026611</v>
       </c>
       <c r="J31" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K31" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L31" t="n">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="M31" t="n">
-        <v>1882.480299960844</v>
+        <v>1839.039425648451</v>
       </c>
       <c r="N31" t="n">
-        <v>1.775668859481812</v>
+        <v>1.645755052566528</v>
       </c>
       <c r="O31" t="n">
-        <v>527</v>
+        <v>568</v>
       </c>
       <c r="P31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1385</v>
+        <v>1427</v>
       </c>
       <c r="R31" t="n">
-        <v>0.8217893392213421</v>
+        <v>0.825425834493576</v>
       </c>
       <c r="S31" t="n">
-        <v>0.6519837749576839</v>
+        <v>0.6103749297454746</v>
       </c>
     </row>
   </sheetData>
